--- a/Aerosol/Aerosol BOM.xlsx
+++ b/Aerosol/Aerosol BOM.xlsx
@@ -1228,7 +1228,7 @@
         <v>1.045</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="L6" s="15">
         <f>J6/(1-K6)</f>
@@ -1287,7 +1287,7 @@
         <v>1.14</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.1</v>
+        <v>0.35</v>
       </c>
       <c r="L7" s="15">
         <f>J7/(1-K7)</f>
